--- a/finance/麦安研营业每日报表_格式化模板.xlsx
+++ b/finance/麦安研营业每日报表_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BA004C-C639-4823-8B10-492107DEE476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D219930B-981B-4920-8446-AB92C3840E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -602,13 +602,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -633,18 +728,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -652,12 +735,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
@@ -678,9 +755,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -690,20 +764,8 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -714,9 +776,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -735,16 +794,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -759,6 +812,63 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -795,40 +905,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1139,39 +1258,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="52"/>
-      <c r="K1" s="50" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="K1" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="52"/>
-      <c r="U1" s="50" t="s">
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="57"/>
+      <c r="U1" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="52"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="57"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1185,7 +1304,7 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="32">
         <v>46174</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -1195,7 +1314,7 @@
       <c r="K3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="32">
         <v>46174</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -1205,7 +1324,7 @@
       <c r="U3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="32">
         <v>46174</v>
       </c>
       <c r="Z3" s="5" t="s">
@@ -1222,1103 +1341,1103 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="53" t="s">
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="55"/>
-      <c r="K5" s="56" t="s">
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="60"/>
+      <c r="K5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="53" t="s">
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="55"/>
-      <c r="U5" s="56" t="s">
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="60"/>
+      <c r="U5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="57"/>
-      <c r="W5" s="57"/>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="53" t="s">
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="63"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="54"/>
-      <c r="AC5" s="55"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="60"/>
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="59"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="56" t="s">
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="56" t="s">
+      <c r="K6" s="64"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="57" t="s">
+      <c r="R6" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="68" t="s">
+      <c r="S6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="59"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="56" t="s">
+      <c r="U6" s="64"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AA6" s="57" t="s">
+      <c r="AA6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="57" t="s">
+      <c r="AB6" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="68" t="s">
+      <c r="AC6" s="67" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="69"/>
-      <c r="K7" s="8" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="68"/>
+      <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="47"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="69"/>
-      <c r="U7" s="8" t="s">
+      <c r="O7" s="33"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="68"/>
+      <c r="U7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="V7" s="9" t="s">
+      <c r="V7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="W7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="X7" s="10" t="s">
+      <c r="X7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="62"/>
-      <c r="AA7" s="63"/>
-      <c r="AB7" s="63"/>
-      <c r="AC7" s="69"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="68"/>
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="44.4" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="18"/>
-      <c r="K8" s="13" t="s">
+      <c r="D8" s="39"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="45"/>
+      <c r="K8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="15" t="s">
+      <c r="L8" s="37"/>
+      <c r="M8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="18"/>
-      <c r="U8" s="13" t="s">
+      <c r="N8" s="39"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="45"/>
+      <c r="U8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="V8" s="30"/>
-      <c r="W8" s="15" t="s">
+      <c r="V8" s="37"/>
+      <c r="W8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="18"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="45"/>
     </row>
     <row r="9" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="71" t="s">
+      <c r="B9" s="77"/>
+      <c r="C9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="18"/>
-      <c r="K9" s="62" t="s">
+      <c r="D9" s="80"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="12"/>
+      <c r="K9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="70"/>
-      <c r="M9" s="71" t="s">
+      <c r="L9" s="77"/>
+      <c r="M9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="N9" s="69"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="18"/>
-      <c r="U9" s="62" t="s">
+      <c r="N9" s="80"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="12"/>
+      <c r="U9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="V9" s="70"/>
-      <c r="W9" s="71" t="s">
+      <c r="V9" s="77"/>
+      <c r="W9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="18"/>
+      <c r="X9" s="80"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="12"/>
     </row>
     <row r="10" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="18"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="18"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="71"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="18"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="12"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="12"/>
+      <c r="U10" s="76"/>
+      <c r="V10" s="77"/>
+      <c r="W10" s="78"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="20"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="73"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="20"/>
-      <c r="U11" s="59"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="73"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="20"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="14"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="14"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="14"/>
     </row>
     <row r="12" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="22"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="22"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-      <c r="AC12" s="22"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="16"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="16"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="16"/>
     </row>
     <row r="13" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="23" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="65"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="23" t="s">
+      <c r="G13" s="70"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="72"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="65"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="23" t="s">
+      <c r="Q13" s="70"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AA13" s="64"/>
-      <c r="AB13" s="64"/>
-      <c r="AC13" s="65"/>
+      <c r="AA13" s="70"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="72"/>
     </row>
     <row r="14" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="26" t="e">
+      <c r="D14" s="19" t="e">
         <f>B14/B8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="19" t="s">
+      <c r="E14" s="33"/>
+      <c r="F14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
-      <c r="K14" s="24" t="s">
+      <c r="G14" s="73"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
+      <c r="K14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="25" t="s">
+      <c r="L14" s="24"/>
+      <c r="M14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="26" t="e">
+      <c r="N14" s="19" t="e">
         <f>L14/L8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O14" s="47"/>
-      <c r="P14" s="19" t="s">
+      <c r="O14" s="33"/>
+      <c r="P14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="67"/>
-      <c r="U14" s="24" t="s">
+      <c r="Q14" s="73"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="75"/>
+      <c r="U14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="V14" s="36"/>
-      <c r="W14" s="25" t="s">
+      <c r="V14" s="24"/>
+      <c r="W14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="X14" s="26" t="e">
+      <c r="X14" s="19" t="e">
         <f>V14/V8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="19" t="s">
+      <c r="Y14" s="33"/>
+      <c r="Z14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="66"/>
-      <c r="AC14" s="67"/>
+      <c r="AA14" s="73"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="75"/>
     </row>
     <row r="15" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="22"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="22"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-      <c r="AC15" s="22"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="16"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="16"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="16"/>
     </row>
     <row r="16" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="23" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="23" t="s">
+      <c r="K16" s="15"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R16" s="27" t="s">
+      <c r="R16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="S16" s="28" t="s">
+      <c r="S16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U16" s="21"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="23" t="s">
+      <c r="U16" s="15"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="AA16" s="27" t="s">
+      <c r="AA16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="AB16" s="27" t="s">
+      <c r="AB16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AC16" s="28" t="s">
+      <c r="AC16" s="49" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+    <row r="17" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="17" t="s">
+      <c r="E17" s="33"/>
+      <c r="F17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="29" t="e">
+      <c r="G17" s="48"/>
+      <c r="H17" s="37" t="e">
         <f>B8/G17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="K17" s="23" t="s">
+      <c r="I17" s="45"/>
+      <c r="K17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="27" t="s">
+      <c r="M17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="28" t="s">
+      <c r="N17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="47"/>
-      <c r="P17" s="17" t="s">
+      <c r="O17" s="33"/>
+      <c r="P17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="29" t="e">
+      <c r="Q17" s="48"/>
+      <c r="R17" s="37" t="e">
         <f>L8/Q17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S17" s="18"/>
-      <c r="U17" s="23" t="s">
+      <c r="S17" s="45"/>
+      <c r="U17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="27" t="s">
+      <c r="V17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="W17" s="27" t="s">
+      <c r="W17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="X17" s="28" t="s">
+      <c r="X17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="Y17" s="47"/>
-      <c r="Z17" s="17" t="s">
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="29" t="e">
+      <c r="AA17" s="48"/>
+      <c r="AB17" s="37" t="e">
         <f>V8/AA17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC17" s="18"/>
+      <c r="AC17" s="45"/>
     </row>
     <row r="18" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="35" t="e">
+      <c r="B18" s="37"/>
+      <c r="C18" s="50" t="e">
         <f>B18/B8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="51">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="17" t="s">
+      <c r="E18" s="33"/>
+      <c r="F18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="30" t="e">
+      <c r="G18" s="10"/>
+      <c r="H18" s="20" t="e">
         <f>B30/G18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="K18" s="17" t="s">
+      <c r="I18" s="12"/>
+      <c r="K18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="30"/>
-      <c r="M18" s="35" t="e">
+      <c r="L18" s="37"/>
+      <c r="M18" s="50" t="e">
         <f>L18/L8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N18" s="42">
+      <c r="N18" s="51">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="O18" s="47"/>
-      <c r="P18" s="17" t="s">
+      <c r="O18" s="33"/>
+      <c r="P18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="30" t="e">
+      <c r="Q18" s="10"/>
+      <c r="R18" s="20" t="e">
         <f>L30/Q18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S18" s="18"/>
-      <c r="U18" s="17" t="s">
+      <c r="S18" s="12"/>
+      <c r="U18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="V18" s="30"/>
-      <c r="W18" s="35" t="e">
+      <c r="V18" s="37"/>
+      <c r="W18" s="50" t="e">
         <f>V18/V8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X18" s="42">
+      <c r="X18" s="51">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Y18" s="47"/>
-      <c r="Z18" s="17" t="s">
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="30" t="e">
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="20" t="e">
         <f>V30/AA18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC18" s="18"/>
+      <c r="AC18" s="12"/>
     </row>
     <row r="19" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="43" t="e">
+      <c r="B19" s="27"/>
+      <c r="C19" s="30" t="e">
         <f>B19/B8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="19" t="s">
+      <c r="E19" s="33"/>
+      <c r="F19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="41"/>
-      <c r="H19" s="31" t="e">
+      <c r="G19" s="29"/>
+      <c r="H19" s="27" t="e">
         <f>B31/G19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="K19" s="19" t="s">
+      <c r="I19" s="14"/>
+      <c r="K19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L19" s="39"/>
-      <c r="M19" s="43" t="e">
+      <c r="L19" s="27"/>
+      <c r="M19" s="30" t="e">
         <f>L19/L8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N19" s="44">
+      <c r="N19" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="O19" s="47"/>
-      <c r="P19" s="19" t="s">
+      <c r="O19" s="33"/>
+      <c r="P19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="31" t="e">
+      <c r="Q19" s="29"/>
+      <c r="R19" s="27" t="e">
         <f>L31/Q19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S19" s="20"/>
-      <c r="U19" s="19" t="s">
+      <c r="S19" s="14"/>
+      <c r="U19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="V19" s="39"/>
-      <c r="W19" s="43" t="e">
+      <c r="V19" s="27"/>
+      <c r="W19" s="30" t="e">
         <f>V19/V8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X19" s="44">
+      <c r="X19" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="19" t="s">
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="31" t="e">
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="27" t="e">
         <f>V31/AA19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC19" s="20"/>
+      <c r="AC19" s="14"/>
     </row>
     <row r="20" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="22"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="22"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="49"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="47"/>
-      <c r="Z20" s="47"/>
-      <c r="AA20" s="48"/>
-      <c r="AB20" s="47"/>
-      <c r="AC20" s="22"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="16"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="16"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="16"/>
     </row>
     <row r="21" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="53" t="s">
+      <c r="A21" s="15"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="55"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="53" t="s">
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="60"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="55"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="53" t="s">
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="60"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="AA21" s="54"/>
-      <c r="AB21" s="54"/>
-      <c r="AC21" s="55"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="59"/>
+      <c r="AC21" s="60"/>
     </row>
     <row r="22" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="23" t="s">
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="57" t="s">
+      <c r="G22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="57"/>
-      <c r="I22" s="28" t="s">
+      <c r="H22" s="69"/>
+      <c r="I22" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="K22" s="53" t="s">
+      <c r="K22" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="23" t="s">
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="57" t="s">
+      <c r="Q22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="57"/>
-      <c r="S22" s="28" t="s">
+      <c r="R22" s="69"/>
+      <c r="S22" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="U22" s="53" t="s">
+      <c r="U22" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="V22" s="54"/>
-      <c r="W22" s="54"/>
-      <c r="X22" s="55"/>
-      <c r="Y22" s="47"/>
-      <c r="Z22" s="23" t="s">
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="AA22" s="57" t="s">
+      <c r="AA22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="AB22" s="57"/>
-      <c r="AC22" s="28" t="s">
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="49" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="17" t="s">
+      <c r="E23" s="33"/>
+      <c r="F23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="18" t="s">
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M23" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="N23" s="45" t="s">
+      <c r="N23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="O23" s="47"/>
-      <c r="P23" s="17" t="s">
+      <c r="O23" s="33"/>
+      <c r="P23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="18" t="s">
+      <c r="Q23" s="81"/>
+      <c r="R23" s="81"/>
+      <c r="S23" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="U23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="V23" s="9" t="s">
+      <c r="V23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="W23" s="9" t="s">
+      <c r="W23" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="X23" s="45" t="s">
+      <c r="X23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="17" t="s">
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="70"/>
-      <c r="AC23" s="18" t="s">
+      <c r="AA23" s="81"/>
+      <c r="AB23" s="81"/>
+      <c r="AC23" s="45" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+      <c r="A24" s="36">
         <v>1</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="17" t="s">
+      <c r="B24" s="52"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="18"/>
-      <c r="K24" s="13">
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="12"/>
+      <c r="K24" s="36">
         <v>1</v>
       </c>
-      <c r="L24" s="32"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="17" t="s">
+      <c r="L24" s="52"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="18"/>
-      <c r="U24" s="13">
+      <c r="Q24" s="77"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="12"/>
+      <c r="U24" s="36">
         <v>1</v>
       </c>
-      <c r="V24" s="32"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="17" t="s">
+      <c r="V24" s="52"/>
+      <c r="W24" s="48"/>
+      <c r="X24" s="53"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="70"/>
-      <c r="AC24" s="18"/>
+      <c r="AA24" s="77"/>
+      <c r="AB24" s="77"/>
+      <c r="AC24" s="12"/>
     </row>
     <row r="25" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
+      <c r="A25" s="9">
         <v>2</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="17" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="18"/>
-      <c r="K25" s="13">
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="12"/>
+      <c r="K25" s="9">
         <v>2</v>
       </c>
-      <c r="L25" s="32"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="17" t="s">
+      <c r="L25" s="21"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="18"/>
-      <c r="U25" s="13">
+      <c r="Q25" s="77"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="12"/>
+      <c r="U25" s="9">
         <v>2</v>
       </c>
-      <c r="V25" s="32"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="47"/>
-      <c r="Z25" s="17" t="s">
+      <c r="V25" s="21"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="70"/>
-      <c r="AC25" s="18"/>
+      <c r="AA25" s="77"/>
+      <c r="AB25" s="77"/>
+      <c r="AC25" s="12"/>
     </row>
     <row r="26" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="9">
         <v>3</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="17" t="s">
+      <c r="B26" s="21"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="18" t="s">
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="9">
         <v>3</v>
       </c>
-      <c r="L26" s="32"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="17" t="s">
+      <c r="L26" s="21"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="18" t="s">
+      <c r="Q26" s="77"/>
+      <c r="R26" s="77"/>
+      <c r="S26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="U26" s="13">
+      <c r="U26" s="9">
         <v>3</v>
       </c>
-      <c r="V26" s="32"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="47"/>
-      <c r="Z26" s="17" t="s">
+      <c r="V26" s="21"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AA26" s="70"/>
-      <c r="AB26" s="70"/>
-      <c r="AC26" s="18" t="s">
+      <c r="AA26" s="77"/>
+      <c r="AB26" s="77"/>
+      <c r="AC26" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
+      <c r="A27" s="9">
         <v>4</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="17" t="s">
+      <c r="B27" s="21"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="18"/>
-      <c r="K27" s="13">
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="12"/>
+      <c r="K27" s="9">
         <v>4</v>
       </c>
-      <c r="L27" s="32"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="17" t="s">
+      <c r="L27" s="21"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="18"/>
-      <c r="U27" s="13">
+      <c r="Q27" s="77"/>
+      <c r="R27" s="77"/>
+      <c r="S27" s="12"/>
+      <c r="U27" s="9">
         <v>4</v>
       </c>
-      <c r="V27" s="32"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="37"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="17" t="s">
+      <c r="V27" s="21"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="70"/>
-      <c r="AC27" s="18"/>
+      <c r="AA27" s="77"/>
+      <c r="AB27" s="77"/>
+      <c r="AC27" s="12"/>
     </row>
     <row r="28" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12">
+      <c r="A28" s="8">
         <v>5</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="19" t="s">
+      <c r="B28" s="22"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="20"/>
-      <c r="K28" s="12">
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="14"/>
+      <c r="K28" s="8">
         <v>5</v>
       </c>
-      <c r="L28" s="33"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="19" t="s">
+      <c r="L28" s="22"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="20"/>
-      <c r="U28" s="12">
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="14"/>
+      <c r="U28" s="8">
         <v>5</v>
       </c>
-      <c r="V28" s="33"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="19" t="s">
+      <c r="V28" s="22"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
-      <c r="AC28" s="20"/>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="14"/>
     </row>
     <row r="29" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="38">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="26">
         <v>0</v>
       </c>
       <c r="U30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V30" s="38">
+      <c r="V30" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2326,19 +2445,19 @@
       <c r="A31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="26">
         <v>0</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31" s="26">
         <v>0</v>
       </c>
       <c r="U31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="V31" s="38">
+      <c r="V31" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2470,39 +2589,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="52"/>
-      <c r="K1" s="50" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="K1" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="52"/>
-      <c r="U1" s="50" t="s">
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="57"/>
+      <c r="U1" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="52"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="57"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2516,7 +2635,7 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="32">
         <v>46175</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -2526,7 +2645,7 @@
       <c r="K3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="32">
         <v>46175</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -2536,7 +2655,7 @@
       <c r="U3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="32">
         <v>46175</v>
       </c>
       <c r="Z3" s="5" t="s">
@@ -2553,1103 +2672,1103 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="53" t="s">
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="55"/>
-      <c r="K5" s="56" t="s">
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="60"/>
+      <c r="K5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="53" t="s">
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="55"/>
-      <c r="U5" s="56" t="s">
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="60"/>
+      <c r="U5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="57"/>
-      <c r="W5" s="57"/>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="53" t="s">
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="63"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="54"/>
-      <c r="AC5" s="55"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="60"/>
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="59"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="56" t="s">
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="56" t="s">
+      <c r="K6" s="64"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="57" t="s">
+      <c r="R6" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="68" t="s">
+      <c r="S6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="59"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="56" t="s">
+      <c r="U6" s="64"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AA6" s="57" t="s">
+      <c r="AA6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="57" t="s">
+      <c r="AB6" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="68" t="s">
+      <c r="AC6" s="67" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="69"/>
-      <c r="K7" s="8" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="68"/>
+      <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="47"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="69"/>
-      <c r="U7" s="8" t="s">
+      <c r="O7" s="33"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="68"/>
+      <c r="U7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="V7" s="9" t="s">
+      <c r="V7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="W7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="X7" s="10" t="s">
+      <c r="X7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="62"/>
-      <c r="AA7" s="63"/>
-      <c r="AB7" s="63"/>
-      <c r="AC7" s="69"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="68"/>
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="44.4" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="18"/>
-      <c r="K8" s="13" t="s">
+      <c r="D8" s="39"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="45"/>
+      <c r="K8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="15" t="s">
+      <c r="L8" s="37"/>
+      <c r="M8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="18"/>
-      <c r="U8" s="13" t="s">
+      <c r="N8" s="39"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="45"/>
+      <c r="U8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="V8" s="30"/>
-      <c r="W8" s="15" t="s">
+      <c r="V8" s="37"/>
+      <c r="W8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="18"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="45"/>
     </row>
     <row r="9" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="71" t="s">
+      <c r="B9" s="77"/>
+      <c r="C9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="18"/>
-      <c r="K9" s="62" t="s">
+      <c r="D9" s="80"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="12"/>
+      <c r="K9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="70"/>
-      <c r="M9" s="71" t="s">
+      <c r="L9" s="77"/>
+      <c r="M9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="N9" s="69"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="18"/>
-      <c r="U9" s="62" t="s">
+      <c r="N9" s="80"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="12"/>
+      <c r="U9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="V9" s="70"/>
-      <c r="W9" s="71" t="s">
+      <c r="V9" s="77"/>
+      <c r="W9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="18"/>
+      <c r="X9" s="80"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="12"/>
     </row>
     <row r="10" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="18"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="18"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="71"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="18"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="12"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="12"/>
+      <c r="U10" s="76"/>
+      <c r="V10" s="77"/>
+      <c r="W10" s="78"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="20"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="73"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="20"/>
-      <c r="U11" s="59"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="73"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="20"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="14"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="14"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="14"/>
     </row>
     <row r="12" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="22"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="22"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-      <c r="AC12" s="22"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="16"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="16"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="16"/>
     </row>
     <row r="13" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="23" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="65"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="23" t="s">
+      <c r="G13" s="70"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="72"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="65"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="23" t="s">
+      <c r="Q13" s="70"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AA13" s="64"/>
-      <c r="AB13" s="64"/>
-      <c r="AC13" s="65"/>
+      <c r="AA13" s="70"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="72"/>
     </row>
     <row r="14" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="26" t="e">
+      <c r="D14" s="19" t="e">
         <f>B14/B8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="19" t="s">
+      <c r="E14" s="33"/>
+      <c r="F14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
-      <c r="K14" s="24" t="s">
+      <c r="G14" s="73"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
+      <c r="K14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="25" t="s">
+      <c r="L14" s="24"/>
+      <c r="M14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="26" t="e">
+      <c r="N14" s="19" t="e">
         <f>L14/L8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O14" s="47"/>
-      <c r="P14" s="19" t="s">
+      <c r="O14" s="33"/>
+      <c r="P14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="67"/>
-      <c r="U14" s="24" t="s">
+      <c r="Q14" s="73"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="75"/>
+      <c r="U14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="V14" s="36"/>
-      <c r="W14" s="25" t="s">
+      <c r="V14" s="24"/>
+      <c r="W14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="X14" s="26" t="e">
+      <c r="X14" s="19" t="e">
         <f>V14/V8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="19" t="s">
+      <c r="Y14" s="33"/>
+      <c r="Z14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="66"/>
-      <c r="AC14" s="67"/>
+      <c r="AA14" s="73"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="75"/>
     </row>
     <row r="15" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="22"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="22"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-      <c r="AC15" s="22"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="16"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="16"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="16"/>
     </row>
     <row r="16" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="23" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="23" t="s">
+      <c r="K16" s="15"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R16" s="27" t="s">
+      <c r="R16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="S16" s="28" t="s">
+      <c r="S16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U16" s="21"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="23" t="s">
+      <c r="U16" s="15"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="AA16" s="27" t="s">
+      <c r="AA16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="AB16" s="27" t="s">
+      <c r="AB16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AC16" s="28" t="s">
+      <c r="AC16" s="49" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+    <row r="17" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="17" t="s">
+      <c r="E17" s="33"/>
+      <c r="F17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="29" t="e">
+      <c r="G17" s="48"/>
+      <c r="H17" s="37" t="e">
         <f>B8/G17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="K17" s="23" t="s">
+      <c r="I17" s="45"/>
+      <c r="K17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="27" t="s">
+      <c r="M17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="28" t="s">
+      <c r="N17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="47"/>
-      <c r="P17" s="17" t="s">
+      <c r="O17" s="33"/>
+      <c r="P17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="29" t="e">
+      <c r="Q17" s="48"/>
+      <c r="R17" s="37" t="e">
         <f>L8/Q17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S17" s="18"/>
-      <c r="U17" s="23" t="s">
+      <c r="S17" s="45"/>
+      <c r="U17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="27" t="s">
+      <c r="V17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="W17" s="27" t="s">
+      <c r="W17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="X17" s="28" t="s">
+      <c r="X17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="Y17" s="47"/>
-      <c r="Z17" s="17" t="s">
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="29" t="e">
+      <c r="AA17" s="48"/>
+      <c r="AB17" s="37" t="e">
         <f>V8/AA17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC17" s="18"/>
+      <c r="AC17" s="45"/>
     </row>
     <row r="18" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="35" t="e">
+      <c r="B18" s="37"/>
+      <c r="C18" s="50" t="e">
         <f>B18/B8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="51">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="17" t="s">
+      <c r="E18" s="33"/>
+      <c r="F18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="30" t="e">
+      <c r="G18" s="10"/>
+      <c r="H18" s="20" t="e">
         <f>B30/G18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="K18" s="17" t="s">
+      <c r="I18" s="12"/>
+      <c r="K18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="30"/>
-      <c r="M18" s="35" t="e">
+      <c r="L18" s="37"/>
+      <c r="M18" s="50" t="e">
         <f>L18/L8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N18" s="42">
+      <c r="N18" s="51">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="O18" s="47"/>
-      <c r="P18" s="17" t="s">
+      <c r="O18" s="33"/>
+      <c r="P18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="30" t="e">
+      <c r="Q18" s="10"/>
+      <c r="R18" s="20" t="e">
         <f>L30/Q18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S18" s="18"/>
-      <c r="U18" s="17" t="s">
+      <c r="S18" s="12"/>
+      <c r="U18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="V18" s="30"/>
-      <c r="W18" s="35" t="e">
+      <c r="V18" s="37"/>
+      <c r="W18" s="50" t="e">
         <f>V18/V8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X18" s="42">
+      <c r="X18" s="51">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Y18" s="47"/>
-      <c r="Z18" s="17" t="s">
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="30" t="e">
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="20" t="e">
         <f>V30/AA18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC18" s="18"/>
+      <c r="AC18" s="12"/>
     </row>
     <row r="19" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="43" t="e">
+      <c r="B19" s="27"/>
+      <c r="C19" s="30" t="e">
         <f>B19/B8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="19" t="s">
+      <c r="E19" s="33"/>
+      <c r="F19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="41"/>
-      <c r="H19" s="31" t="e">
+      <c r="G19" s="29"/>
+      <c r="H19" s="27" t="e">
         <f>B31/G19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="K19" s="19" t="s">
+      <c r="I19" s="14"/>
+      <c r="K19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L19" s="39"/>
-      <c r="M19" s="43" t="e">
+      <c r="L19" s="27"/>
+      <c r="M19" s="30" t="e">
         <f>L19/L8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N19" s="44">
+      <c r="N19" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="O19" s="47"/>
-      <c r="P19" s="19" t="s">
+      <c r="O19" s="33"/>
+      <c r="P19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="31" t="e">
+      <c r="Q19" s="29"/>
+      <c r="R19" s="27" t="e">
         <f>L31/Q19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S19" s="20"/>
-      <c r="U19" s="19" t="s">
+      <c r="S19" s="14"/>
+      <c r="U19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="V19" s="39"/>
-      <c r="W19" s="43" t="e">
+      <c r="V19" s="27"/>
+      <c r="W19" s="30" t="e">
         <f>V19/V8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X19" s="44">
+      <c r="X19" s="31">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="19" t="s">
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="31" t="e">
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="27" t="e">
         <f>V31/AA19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC19" s="20"/>
+      <c r="AC19" s="14"/>
     </row>
     <row r="20" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="22"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="22"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="49"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="47"/>
-      <c r="Z20" s="47"/>
-      <c r="AA20" s="48"/>
-      <c r="AB20" s="47"/>
-      <c r="AC20" s="22"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="16"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="16"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="16"/>
     </row>
     <row r="21" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="53" t="s">
+      <c r="A21" s="15"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="55"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="53" t="s">
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="60"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="55"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="53" t="s">
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="60"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="AA21" s="54"/>
-      <c r="AB21" s="54"/>
-      <c r="AC21" s="55"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="59"/>
+      <c r="AC21" s="60"/>
     </row>
     <row r="22" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="23" t="s">
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="57" t="s">
+      <c r="G22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="57"/>
-      <c r="I22" s="28" t="s">
+      <c r="H22" s="69"/>
+      <c r="I22" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="K22" s="53" t="s">
+      <c r="K22" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="23" t="s">
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="57" t="s">
+      <c r="Q22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="57"/>
-      <c r="S22" s="28" t="s">
+      <c r="R22" s="69"/>
+      <c r="S22" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="U22" s="53" t="s">
+      <c r="U22" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="V22" s="54"/>
-      <c r="W22" s="54"/>
-      <c r="X22" s="55"/>
-      <c r="Y22" s="47"/>
-      <c r="Z22" s="23" t="s">
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="AA22" s="57" t="s">
+      <c r="AA22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="AB22" s="57"/>
-      <c r="AC22" s="28" t="s">
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="49" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="17" t="s">
+      <c r="E23" s="33"/>
+      <c r="F23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="18" t="s">
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M23" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="N23" s="45" t="s">
+      <c r="N23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="O23" s="47"/>
-      <c r="P23" s="17" t="s">
+      <c r="O23" s="33"/>
+      <c r="P23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="18" t="s">
+      <c r="Q23" s="81"/>
+      <c r="R23" s="81"/>
+      <c r="S23" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="U23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="V23" s="9" t="s">
+      <c r="V23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="W23" s="9" t="s">
+      <c r="W23" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="X23" s="45" t="s">
+      <c r="X23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="17" t="s">
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="70"/>
-      <c r="AC23" s="18" t="s">
+      <c r="AA23" s="81"/>
+      <c r="AB23" s="81"/>
+      <c r="AC23" s="45" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+      <c r="A24" s="36">
         <v>1</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="17" t="s">
+      <c r="B24" s="52"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="18"/>
-      <c r="K24" s="13">
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="12"/>
+      <c r="K24" s="36">
         <v>1</v>
       </c>
-      <c r="L24" s="32"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="17" t="s">
+      <c r="L24" s="52"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="18"/>
-      <c r="U24" s="13">
+      <c r="Q24" s="77"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="12"/>
+      <c r="U24" s="36">
         <v>1</v>
       </c>
-      <c r="V24" s="32"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="17" t="s">
+      <c r="V24" s="52"/>
+      <c r="W24" s="48"/>
+      <c r="X24" s="53"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="70"/>
-      <c r="AC24" s="18"/>
+      <c r="AA24" s="77"/>
+      <c r="AB24" s="77"/>
+      <c r="AC24" s="12"/>
     </row>
     <row r="25" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
+      <c r="A25" s="9">
         <v>2</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="17" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="18"/>
-      <c r="K25" s="13">
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="12"/>
+      <c r="K25" s="9">
         <v>2</v>
       </c>
-      <c r="L25" s="32"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="17" t="s">
+      <c r="L25" s="21"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="18"/>
-      <c r="U25" s="13">
+      <c r="Q25" s="77"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="12"/>
+      <c r="U25" s="9">
         <v>2</v>
       </c>
-      <c r="V25" s="32"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="47"/>
-      <c r="Z25" s="17" t="s">
+      <c r="V25" s="21"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="70"/>
-      <c r="AC25" s="18"/>
+      <c r="AA25" s="77"/>
+      <c r="AB25" s="77"/>
+      <c r="AC25" s="12"/>
     </row>
     <row r="26" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="9">
         <v>3</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="17" t="s">
+      <c r="B26" s="21"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="18" t="s">
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="9">
         <v>3</v>
       </c>
-      <c r="L26" s="32"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="17" t="s">
+      <c r="L26" s="21"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="18" t="s">
+      <c r="Q26" s="77"/>
+      <c r="R26" s="77"/>
+      <c r="S26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="U26" s="13">
+      <c r="U26" s="9">
         <v>3</v>
       </c>
-      <c r="V26" s="32"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="47"/>
-      <c r="Z26" s="17" t="s">
+      <c r="V26" s="21"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AA26" s="70"/>
-      <c r="AB26" s="70"/>
-      <c r="AC26" s="18" t="s">
+      <c r="AA26" s="77"/>
+      <c r="AB26" s="77"/>
+      <c r="AC26" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
+      <c r="A27" s="9">
         <v>4</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="17" t="s">
+      <c r="B27" s="21"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="18"/>
-      <c r="K27" s="13">
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="12"/>
+      <c r="K27" s="9">
         <v>4</v>
       </c>
-      <c r="L27" s="32"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="17" t="s">
+      <c r="L27" s="21"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="18"/>
-      <c r="U27" s="13">
+      <c r="Q27" s="77"/>
+      <c r="R27" s="77"/>
+      <c r="S27" s="12"/>
+      <c r="U27" s="9">
         <v>4</v>
       </c>
-      <c r="V27" s="32"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="37"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="17" t="s">
+      <c r="V27" s="21"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="70"/>
-      <c r="AC27" s="18"/>
+      <c r="AA27" s="77"/>
+      <c r="AB27" s="77"/>
+      <c r="AC27" s="12"/>
     </row>
     <row r="28" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12">
+      <c r="A28" s="8">
         <v>5</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="19" t="s">
+      <c r="B28" s="22"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="20"/>
-      <c r="K28" s="12">
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="14"/>
+      <c r="K28" s="8">
         <v>5</v>
       </c>
-      <c r="L28" s="33"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="19" t="s">
+      <c r="L28" s="22"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="20"/>
-      <c r="U28" s="12">
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="14"/>
+      <c r="U28" s="8">
         <v>5</v>
       </c>
-      <c r="V28" s="33"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="19" t="s">
+      <c r="V28" s="22"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
-      <c r="AC28" s="20"/>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="14"/>
     </row>
     <row r="29" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="38">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="26">
         <v>0</v>
       </c>
       <c r="U30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V30" s="38">
+      <c r="V30" s="26">
         <v>0</v>
       </c>
     </row>
@@ -3657,19 +3776,19 @@
       <c r="A31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="26">
         <v>0</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31" s="26">
         <v>0</v>
       </c>
       <c r="U31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="V31" s="38">
+      <c r="V31" s="26">
         <v>0</v>
       </c>
     </row>

--- a/finance/麦安研营业每日报表_格式化模板.xlsx
+++ b/finance/麦安研营业每日报表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D219930B-981B-4920-8446-AB92C3840E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EBE132-79CF-48E7-B82B-5DAE77CCB48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="麦安研3店营业日报表--6.1" sheetId="84" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="57">
   <si>
     <t>东方宝泰营业日报表</t>
   </si>
@@ -229,6 +229,18 @@
   </si>
   <si>
     <t>顺德杏坛店营业日报表</t>
+  </si>
+  <si>
+    <t>19：00-19：59</t>
+  </si>
+  <si>
+    <t>20：00-20：59</t>
+  </si>
+  <si>
+    <t>21：00-21：59</t>
+  </si>
+  <si>
+    <t>22：00-22：59</t>
   </si>
 </sst>
 </file>
@@ -869,6 +881,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -878,15 +911,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -911,9 +935,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -921,15 +942,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,39 +1270,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="57"/>
-      <c r="K1" s="55" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="64"/>
+      <c r="K1" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="57"/>
-      <c r="U1" s="55" t="s">
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="64"/>
+      <c r="U1" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="57"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="64"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1341,12 +1353,12 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="63"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67"/>
       <c r="E5" s="33"/>
       <c r="F5" s="58" t="s">
         <v>48</v>
@@ -1354,12 +1366,12 @@
       <c r="G5" s="59"/>
       <c r="H5" s="59"/>
       <c r="I5" s="60"/>
-      <c r="K5" s="61" t="s">
+      <c r="K5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="63"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
       <c r="O5" s="33"/>
       <c r="P5" s="58" t="s">
         <v>48</v>
@@ -1367,12 +1379,12 @@
       <c r="Q5" s="59"/>
       <c r="R5" s="59"/>
       <c r="S5" s="60"/>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="63"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="67"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="58" t="s">
         <v>48</v>
@@ -1382,55 +1394,55 @@
       <c r="AC5" s="60"/>
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="33"/>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="67" t="s">
+      <c r="I6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="64"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="66"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="70"/>
       <c r="O6" s="33"/>
-      <c r="P6" s="61" t="s">
+      <c r="P6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="62" t="s">
+      <c r="Q6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="62" t="s">
+      <c r="R6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="67" t="s">
+      <c r="S6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="64"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="66"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="70"/>
       <c r="Y6" s="33"/>
-      <c r="Z6" s="61" t="s">
+      <c r="Z6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="AA6" s="62" t="s">
+      <c r="AA6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="62" t="s">
+      <c r="AB6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="67" t="s">
+      <c r="AC6" s="71" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1448,10 +1460,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="33"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="72"/>
       <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
@@ -1465,10 +1477,10 @@
         <v>7</v>
       </c>
       <c r="O7" s="33"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="72"/>
       <c r="U7" s="40" t="s">
         <v>6</v>
       </c>
@@ -1482,10 +1494,10 @@
         <v>7</v>
       </c>
       <c r="Y7" s="33"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
-      <c r="AC7" s="68"/>
+      <c r="Z7" s="68"/>
+      <c r="AA7" s="69"/>
+      <c r="AB7" s="69"/>
+      <c r="AC7" s="72"/>
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="44.4" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
@@ -1599,28 +1611,28 @@
       <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="74"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="79"/>
-      <c r="D11" s="68"/>
+      <c r="D11" s="72"/>
       <c r="E11" s="33"/>
       <c r="F11" s="13"/>
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="14"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="74"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="56"/>
       <c r="M11" s="79"/>
-      <c r="N11" s="68"/>
+      <c r="N11" s="72"/>
       <c r="O11" s="33"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="27"/>
       <c r="R11" s="27"/>
       <c r="S11" s="14"/>
-      <c r="U11" s="64"/>
-      <c r="V11" s="74"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="56"/>
       <c r="W11" s="79"/>
-      <c r="X11" s="68"/>
+      <c r="X11" s="72"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="13"/>
       <c r="AA11" s="27"/>
@@ -1665,9 +1677,9 @@
       <c r="F13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
       <c r="K13" s="15"/>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
@@ -1676,9 +1688,9 @@
       <c r="P13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="72"/>
+      <c r="Q13" s="73"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="75"/>
       <c r="U13" s="15"/>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
@@ -1687,9 +1699,9 @@
       <c r="Z13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AA13" s="70"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="72"/>
+      <c r="AA13" s="73"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="75"/>
     </row>
     <row r="14" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
@@ -1707,9 +1719,9 @@
       <c r="F14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="75"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="57"/>
       <c r="K14" s="17" t="s">
         <v>13</v>
       </c>
@@ -1725,9 +1737,9 @@
       <c r="P14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="75"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="57"/>
       <c r="U14" s="17" t="s">
         <v>13</v>
       </c>
@@ -1743,9 +1755,9 @@
       <c r="Z14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AA14" s="73"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="75"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="57"/>
     </row>
     <row r="15" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
@@ -2102,10 +2114,10 @@
       <c r="F22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="69" t="s">
+      <c r="G22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="69"/>
+      <c r="H22" s="61"/>
       <c r="I22" s="49" t="s">
         <v>33</v>
       </c>
@@ -2119,10 +2131,10 @@
       <c r="P22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="69" t="s">
+      <c r="Q22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="69"/>
+      <c r="R22" s="61"/>
       <c r="S22" s="49" t="s">
         <v>33</v>
       </c>
@@ -2136,10 +2148,10 @@
       <c r="Z22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="AA22" s="69" t="s">
+      <c r="AA22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="AB22" s="69"/>
+      <c r="AB22" s="61"/>
       <c r="AC22" s="49" t="s">
         <v>33</v>
       </c>
@@ -2180,7 +2192,7 @@
       </c>
       <c r="O23" s="33"/>
       <c r="P23" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q23" s="81"/>
       <c r="R23" s="81"/>
@@ -2201,7 +2213,7 @@
       </c>
       <c r="Y23" s="33"/>
       <c r="Z23" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA23" s="81"/>
       <c r="AB23" s="81"/>
@@ -2231,7 +2243,7 @@
       <c r="N24" s="53"/>
       <c r="O24" s="33"/>
       <c r="P24" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q24" s="77"/>
       <c r="R24" s="77"/>
@@ -2244,7 +2256,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA24" s="77"/>
       <c r="AB24" s="77"/>
@@ -2272,7 +2284,7 @@
       <c r="N25" s="25"/>
       <c r="O25" s="33"/>
       <c r="P25" s="11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q25" s="77"/>
       <c r="R25" s="77"/>
@@ -2285,7 +2297,7 @@
       <c r="X25" s="25"/>
       <c r="Y25" s="33"/>
       <c r="Z25" s="11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AA25" s="77"/>
       <c r="AB25" s="77"/>
@@ -2315,7 +2327,7 @@
       <c r="N26" s="25"/>
       <c r="O26" s="33"/>
       <c r="P26" s="11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Q26" s="77"/>
       <c r="R26" s="77"/>
@@ -2330,7 +2342,7 @@
       <c r="X26" s="25"/>
       <c r="Y26" s="33"/>
       <c r="Z26" s="11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AA26" s="77"/>
       <c r="AB26" s="77"/>
@@ -2360,7 +2372,7 @@
       <c r="N27" s="25"/>
       <c r="O27" s="33"/>
       <c r="P27" s="11" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q27" s="77"/>
       <c r="R27" s="77"/>
@@ -2373,7 +2385,7 @@
       <c r="X27" s="25"/>
       <c r="Y27" s="33"/>
       <c r="Z27" s="11" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA27" s="77"/>
       <c r="AB27" s="77"/>
@@ -2390,8 +2402,8 @@
       <c r="F28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
       <c r="I28" s="14"/>
       <c r="K28" s="8">
         <v>5</v>
@@ -2401,10 +2413,10 @@
       <c r="N28" s="28"/>
       <c r="O28" s="23"/>
       <c r="P28" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
+        <v>56</v>
+      </c>
+      <c r="Q28" s="56"/>
+      <c r="R28" s="56"/>
       <c r="S28" s="14"/>
       <c r="U28" s="8">
         <v>5</v>
@@ -2414,10 +2426,10 @@
       <c r="X28" s="28"/>
       <c r="Y28" s="23"/>
       <c r="Z28" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA28" s="74"/>
-      <c r="AB28" s="74"/>
+        <v>56</v>
+      </c>
+      <c r="AA28" s="56"/>
+      <c r="AB28" s="56"/>
       <c r="AC28" s="14"/>
     </row>
     <row r="29" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2478,6 +2490,56 @@
     <row r="46" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="U1:AC1"/>
+    <mergeCell ref="U5:X6"/>
+    <mergeCell ref="Z5:AC5"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:V11"/>
+    <mergeCell ref="W9:W11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="AA13:AC13"/>
     <mergeCell ref="AA14:AC14"/>
     <mergeCell ref="Z21:AC21"/>
     <mergeCell ref="U22:X22"/>
@@ -2494,56 +2556,6 @@
     <mergeCell ref="P21:S21"/>
     <mergeCell ref="K22:N22"/>
     <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:V11"/>
-    <mergeCell ref="W9:W11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="AA13:AC13"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="A5:D6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="U1:AC1"/>
-    <mergeCell ref="U5:X6"/>
-    <mergeCell ref="Z5:AC5"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AB6:AB7"/>
-    <mergeCell ref="AC6:AC7"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2589,39 +2601,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="57"/>
-      <c r="K1" s="55" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="64"/>
+      <c r="K1" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="57"/>
-      <c r="U1" s="55" t="s">
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="64"/>
+      <c r="U1" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="57"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="64"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2672,12 +2684,12 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="63"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67"/>
       <c r="E5" s="33"/>
       <c r="F5" s="58" t="s">
         <v>48</v>
@@ -2685,12 +2697,12 @@
       <c r="G5" s="59"/>
       <c r="H5" s="59"/>
       <c r="I5" s="60"/>
-      <c r="K5" s="61" t="s">
+      <c r="K5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="63"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
       <c r="O5" s="33"/>
       <c r="P5" s="58" t="s">
         <v>48</v>
@@ -2698,12 +2710,12 @@
       <c r="Q5" s="59"/>
       <c r="R5" s="59"/>
       <c r="S5" s="60"/>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="63"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="67"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="58" t="s">
         <v>48</v>
@@ -2713,55 +2725,55 @@
       <c r="AC5" s="60"/>
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="33"/>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="67" t="s">
+      <c r="I6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="64"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="66"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="70"/>
       <c r="O6" s="33"/>
-      <c r="P6" s="61" t="s">
+      <c r="P6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="62" t="s">
+      <c r="Q6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="62" t="s">
+      <c r="R6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="67" t="s">
+      <c r="S6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="64"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="66"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="70"/>
       <c r="Y6" s="33"/>
-      <c r="Z6" s="61" t="s">
+      <c r="Z6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="AA6" s="62" t="s">
+      <c r="AA6" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="62" t="s">
+      <c r="AB6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="67" t="s">
+      <c r="AC6" s="71" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2779,10 +2791,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="33"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="72"/>
       <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
@@ -2796,10 +2808,10 @@
         <v>7</v>
       </c>
       <c r="O7" s="33"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="72"/>
       <c r="U7" s="40" t="s">
         <v>6</v>
       </c>
@@ -2813,10 +2825,10 @@
         <v>7</v>
       </c>
       <c r="Y7" s="33"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
-      <c r="AC7" s="68"/>
+      <c r="Z7" s="68"/>
+      <c r="AA7" s="69"/>
+      <c r="AB7" s="69"/>
+      <c r="AC7" s="72"/>
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="44.4" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
@@ -2930,28 +2942,28 @@
       <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="74"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="79"/>
-      <c r="D11" s="68"/>
+      <c r="D11" s="72"/>
       <c r="E11" s="33"/>
       <c r="F11" s="13"/>
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="14"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="74"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="56"/>
       <c r="M11" s="79"/>
-      <c r="N11" s="68"/>
+      <c r="N11" s="72"/>
       <c r="O11" s="33"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="27"/>
       <c r="R11" s="27"/>
       <c r="S11" s="14"/>
-      <c r="U11" s="64"/>
-      <c r="V11" s="74"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="56"/>
       <c r="W11" s="79"/>
-      <c r="X11" s="68"/>
+      <c r="X11" s="72"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="13"/>
       <c r="AA11" s="27"/>
@@ -2996,9 +3008,9 @@
       <c r="F13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
       <c r="K13" s="15"/>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
@@ -3007,9 +3019,9 @@
       <c r="P13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="72"/>
+      <c r="Q13" s="73"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="75"/>
       <c r="U13" s="15"/>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
@@ -3018,9 +3030,9 @@
       <c r="Z13" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AA13" s="70"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="72"/>
+      <c r="AA13" s="73"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="75"/>
     </row>
     <row r="14" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
@@ -3038,9 +3050,9 @@
       <c r="F14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="75"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="57"/>
       <c r="K14" s="17" t="s">
         <v>13</v>
       </c>
@@ -3056,9 +3068,9 @@
       <c r="P14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="75"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="57"/>
       <c r="U14" s="17" t="s">
         <v>13</v>
       </c>
@@ -3074,9 +3086,9 @@
       <c r="Z14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AA14" s="73"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="75"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="57"/>
     </row>
     <row r="15" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
@@ -3433,10 +3445,10 @@
       <c r="F22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="69" t="s">
+      <c r="G22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="69"/>
+      <c r="H22" s="61"/>
       <c r="I22" s="49" t="s">
         <v>33</v>
       </c>
@@ -3450,10 +3462,10 @@
       <c r="P22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="69" t="s">
+      <c r="Q22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="69"/>
+      <c r="R22" s="61"/>
       <c r="S22" s="49" t="s">
         <v>33</v>
       </c>
@@ -3467,10 +3479,10 @@
       <c r="Z22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="AA22" s="69" t="s">
+      <c r="AA22" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="AB22" s="69"/>
+      <c r="AB22" s="61"/>
       <c r="AC22" s="49" t="s">
         <v>33</v>
       </c>
@@ -3511,7 +3523,7 @@
       </c>
       <c r="O23" s="33"/>
       <c r="P23" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q23" s="81"/>
       <c r="R23" s="81"/>
@@ -3532,7 +3544,7 @@
       </c>
       <c r="Y23" s="33"/>
       <c r="Z23" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA23" s="81"/>
       <c r="AB23" s="81"/>
@@ -3562,7 +3574,7 @@
       <c r="N24" s="53"/>
       <c r="O24" s="33"/>
       <c r="P24" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q24" s="77"/>
       <c r="R24" s="77"/>
@@ -3575,7 +3587,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA24" s="77"/>
       <c r="AB24" s="77"/>
@@ -3603,7 +3615,7 @@
       <c r="N25" s="25"/>
       <c r="O25" s="33"/>
       <c r="P25" s="11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q25" s="77"/>
       <c r="R25" s="77"/>
@@ -3616,7 +3628,7 @@
       <c r="X25" s="25"/>
       <c r="Y25" s="33"/>
       <c r="Z25" s="11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AA25" s="77"/>
       <c r="AB25" s="77"/>
@@ -3646,7 +3658,7 @@
       <c r="N26" s="25"/>
       <c r="O26" s="33"/>
       <c r="P26" s="11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Q26" s="77"/>
       <c r="R26" s="77"/>
@@ -3661,7 +3673,7 @@
       <c r="X26" s="25"/>
       <c r="Y26" s="33"/>
       <c r="Z26" s="11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AA26" s="77"/>
       <c r="AB26" s="77"/>
@@ -3691,7 +3703,7 @@
       <c r="N27" s="25"/>
       <c r="O27" s="33"/>
       <c r="P27" s="11" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q27" s="77"/>
       <c r="R27" s="77"/>
@@ -3704,7 +3716,7 @@
       <c r="X27" s="25"/>
       <c r="Y27" s="33"/>
       <c r="Z27" s="11" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA27" s="77"/>
       <c r="AB27" s="77"/>
@@ -3721,8 +3733,8 @@
       <c r="F28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
       <c r="I28" s="14"/>
       <c r="K28" s="8">
         <v>5</v>
@@ -3732,10 +3744,10 @@
       <c r="N28" s="28"/>
       <c r="O28" s="23"/>
       <c r="P28" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
+        <v>56</v>
+      </c>
+      <c r="Q28" s="56"/>
+      <c r="R28" s="56"/>
       <c r="S28" s="14"/>
       <c r="U28" s="8">
         <v>5</v>
@@ -3745,10 +3757,10 @@
       <c r="X28" s="28"/>
       <c r="Y28" s="23"/>
       <c r="Z28" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA28" s="74"/>
-      <c r="AB28" s="74"/>
+        <v>56</v>
+      </c>
+      <c r="AA28" s="56"/>
+      <c r="AB28" s="56"/>
       <c r="AC28" s="14"/>
     </row>
     <row r="29" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3809,56 +3821,6 @@
     <row r="46" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="Z21:AC21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="AA13:AC13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="AA14:AC14"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:V11"/>
-    <mergeCell ref="W9:W11"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AB6:AB7"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="K9:K11"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="K1:S1"/>
@@ -3875,6 +3837,56 @@
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="AA13:AC13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:V11"/>
+    <mergeCell ref="W9:W11"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="Z21:AC21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="AA28:AB28"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/finance/麦安研营业每日报表_格式化模板.xlsx
+++ b/finance/麦安研营业每日报表_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EBE132-79CF-48E7-B82B-5DAE77CCB48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F61EE5-4BED-4EA5-8712-8E66F3A57923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,12 +51,6 @@
   </si>
   <si>
     <t>余下天数每日应达实收</t>
-  </si>
-  <si>
-    <t>本周实收</t>
-  </si>
-  <si>
-    <t>周目标</t>
   </si>
   <si>
     <t>充值目标</t>
@@ -241,6 +235,14 @@
   </si>
   <si>
     <t>22：00-22：59</t>
+  </si>
+  <si>
+    <t>本月实收</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>月目标</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -881,6 +883,60 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -888,60 +944,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1270,39 +1272,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="64"/>
-      <c r="K1" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64"/>
-      <c r="U1" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="64"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="K1" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="57"/>
+      <c r="U1" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="57"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1320,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I3" s="6"/>
       <c r="K3" s="4" t="s">
@@ -1330,7 +1332,7 @@
         <v>46174</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S3" s="6"/>
       <c r="U3" s="4" t="s">
@@ -1340,7 +1342,7 @@
         <v>46174</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC3" s="6"/>
     </row>
@@ -1353,96 +1355,96 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="67"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="33"/>
       <c r="F5" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G5" s="59"/>
       <c r="H5" s="59"/>
       <c r="I5" s="60"/>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="63"/>
       <c r="O5" s="33"/>
       <c r="P5" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q5" s="59"/>
       <c r="R5" s="59"/>
       <c r="S5" s="60"/>
-      <c r="U5" s="65" t="s">
+      <c r="U5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="63"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA5" s="59"/>
       <c r="AB5" s="59"/>
       <c r="AC5" s="60"/>
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
       <c r="E6" s="33"/>
-      <c r="F6" s="65" t="s">
+      <c r="F6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="71" t="s">
+      <c r="G6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="70"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
       <c r="O6" s="33"/>
-      <c r="P6" s="65" t="s">
+      <c r="P6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="68"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="66"/>
       <c r="Y6" s="33"/>
-      <c r="Z6" s="65" t="s">
+      <c r="Z6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AA6" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC6" s="71" t="s">
+      <c r="AA6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB6" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC6" s="67" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1460,10 +1462,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="33"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="72"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="68"/>
       <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
@@ -1477,10 +1479,10 @@
         <v>7</v>
       </c>
       <c r="O7" s="33"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="72"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="68"/>
       <c r="U7" s="40" t="s">
         <v>6</v>
       </c>
@@ -1494,10 +1496,10 @@
         <v>7</v>
       </c>
       <c r="Y7" s="33"/>
-      <c r="Z7" s="68"/>
-      <c r="AA7" s="69"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="72"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="68"/>
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="44.4" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
@@ -1542,11 +1544,11 @@
     </row>
     <row r="9" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
       <c r="A9" s="76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B9" s="77"/>
       <c r="C9" s="78" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D9" s="80"/>
       <c r="E9" s="33"/>
@@ -1555,11 +1557,11 @@
       <c r="H9" s="20"/>
       <c r="I9" s="12"/>
       <c r="K9" s="76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="L9" s="77"/>
       <c r="M9" s="78" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="N9" s="80"/>
       <c r="O9" s="33"/>
@@ -1568,11 +1570,11 @@
       <c r="R9" s="20"/>
       <c r="S9" s="12"/>
       <c r="U9" s="76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="V9" s="77"/>
       <c r="W9" s="78" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="X9" s="80"/>
       <c r="Y9" s="33"/>
@@ -1611,28 +1613,28 @@
       <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="68"/>
-      <c r="B11" s="56"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="74"/>
       <c r="C11" s="79"/>
-      <c r="D11" s="72"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="33"/>
       <c r="F11" s="13"/>
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="14"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="56"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="74"/>
       <c r="M11" s="79"/>
-      <c r="N11" s="72"/>
+      <c r="N11" s="68"/>
       <c r="O11" s="33"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="27"/>
       <c r="R11" s="27"/>
       <c r="S11" s="14"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="56"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="74"/>
       <c r="W11" s="79"/>
-      <c r="X11" s="72"/>
+      <c r="X11" s="68"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="13"/>
       <c r="AA11" s="27"/>
@@ -1675,41 +1677,41 @@
       <c r="D13" s="33"/>
       <c r="E13" s="33"/>
       <c r="F13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="75"/>
+        <v>10</v>
+      </c>
+      <c r="G13" s="70"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="72"/>
       <c r="K13" s="15"/>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
       <c r="N13" s="33"/>
       <c r="O13" s="33"/>
       <c r="P13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="74"/>
-      <c r="S13" s="75"/>
+        <v>10</v>
+      </c>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
       <c r="U13" s="15"/>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
       <c r="Y13" s="33"/>
       <c r="Z13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA13" s="73"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="75"/>
+        <v>10</v>
+      </c>
+      <c r="AA13" s="70"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="72"/>
     </row>
     <row r="14" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" s="19" t="e">
         <f>B14/B8</f>
@@ -1717,17 +1719,17 @@
       </c>
       <c r="E14" s="33"/>
       <c r="F14" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="55"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="57"/>
+        <v>13</v>
+      </c>
+      <c r="G14" s="73"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
       <c r="K14" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L14" s="24"/>
       <c r="M14" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N14" s="19" t="e">
         <f>L14/L8</f>
@@ -1735,17 +1737,17 @@
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="57"/>
+        <v>13</v>
+      </c>
+      <c r="Q14" s="73"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="75"/>
       <c r="U14" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V14" s="24"/>
       <c r="W14" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X14" s="19" t="e">
         <f>V14/V8</f>
@@ -1753,11 +1755,11 @@
       </c>
       <c r="Y14" s="33"/>
       <c r="Z14" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA14" s="55"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="57"/>
+        <v>13</v>
+      </c>
+      <c r="AA14" s="73"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="75"/>
     </row>
     <row r="15" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
@@ -1795,16 +1797,16 @@
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="I16" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>19</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="33"/>
@@ -1812,16 +1814,16 @@
       <c r="N16" s="33"/>
       <c r="O16" s="33"/>
       <c r="P16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="R16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="18" t="s">
+      <c r="S16" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="S16" s="49" t="s">
-        <v>19</v>
       </c>
       <c r="U16" s="15"/>
       <c r="V16" s="33"/>
@@ -1829,34 +1831,34 @@
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
       <c r="Z16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="AA16" s="18" t="s">
+      <c r="AC16" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="AB16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC16" s="49" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="D17" s="49" t="s">
         <v>21</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>23</v>
       </c>
       <c r="E17" s="33"/>
       <c r="F17" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="48"/>
       <c r="H17" s="37" t="e">
@@ -1865,20 +1867,20 @@
       </c>
       <c r="I17" s="45"/>
       <c r="K17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="N17" s="49" t="s">
         <v>21</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="49" t="s">
-        <v>23</v>
       </c>
       <c r="O17" s="33"/>
       <c r="P17" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="48"/>
       <c r="R17" s="37" t="e">
@@ -1887,20 +1889,20 @@
       </c>
       <c r="S17" s="45"/>
       <c r="U17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="W17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="18" t="s">
+      <c r="X17" s="49" t="s">
         <v>21</v>
-      </c>
-      <c r="W17" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="X17" s="49" t="s">
-        <v>23</v>
       </c>
       <c r="Y17" s="33"/>
       <c r="Z17" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA17" s="48"/>
       <c r="AB17" s="37" t="e">
@@ -1911,7 +1913,7 @@
     </row>
     <row r="18" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="37"/>
       <c r="C18" s="50" t="e">
@@ -1923,7 +1925,7 @@
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="20" t="e">
@@ -1932,7 +1934,7 @@
       </c>
       <c r="I18" s="12"/>
       <c r="K18" s="44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L18" s="37"/>
       <c r="M18" s="50" t="e">
@@ -1944,7 +1946,7 @@
       </c>
       <c r="O18" s="33"/>
       <c r="P18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="10"/>
       <c r="R18" s="20" t="e">
@@ -1953,7 +1955,7 @@
       </c>
       <c r="S18" s="12"/>
       <c r="U18" s="44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V18" s="37"/>
       <c r="W18" s="50" t="e">
@@ -1965,7 +1967,7 @@
       </c>
       <c r="Y18" s="33"/>
       <c r="Z18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA18" s="10"/>
       <c r="AB18" s="20" t="e">
@@ -1976,7 +1978,7 @@
     </row>
     <row r="19" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="30" t="e">
@@ -1988,7 +1990,7 @@
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" s="29"/>
       <c r="H19" s="27" t="e">
@@ -1997,7 +1999,7 @@
       </c>
       <c r="I19" s="14"/>
       <c r="K19" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L19" s="27"/>
       <c r="M19" s="30" t="e">
@@ -2009,7 +2011,7 @@
       </c>
       <c r="O19" s="33"/>
       <c r="P19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q19" s="29"/>
       <c r="R19" s="27" t="e">
@@ -2018,7 +2020,7 @@
       </c>
       <c r="S19" s="14"/>
       <c r="U19" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V19" s="27"/>
       <c r="W19" s="30" t="e">
@@ -2030,7 +2032,7 @@
       </c>
       <c r="Y19" s="33"/>
       <c r="Z19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA19" s="29"/>
       <c r="AB19" s="27" t="e">
@@ -2075,7 +2077,7 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
       <c r="F21" s="58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" s="59"/>
       <c r="H21" s="59"/>
@@ -2086,7 +2088,7 @@
       <c r="N21" s="33"/>
       <c r="O21" s="33"/>
       <c r="P21" s="58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q21" s="59"/>
       <c r="R21" s="59"/>
@@ -2097,7 +2099,7 @@
       <c r="X21" s="33"/>
       <c r="Y21" s="33"/>
       <c r="Z21" s="58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA21" s="59"/>
       <c r="AB21" s="59"/>
@@ -2105,60 +2107,60 @@
     </row>
     <row r="22" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
       <c r="D22" s="60"/>
       <c r="E22" s="33"/>
       <c r="F22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="69"/>
+      <c r="I22" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="61"/>
-      <c r="I22" s="49" t="s">
-        <v>33</v>
-      </c>
       <c r="K22" s="58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L22" s="59"/>
       <c r="M22" s="59"/>
       <c r="N22" s="60"/>
       <c r="O22" s="33"/>
       <c r="P22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" s="69"/>
+      <c r="S22" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="61"/>
-      <c r="S22" s="49" t="s">
-        <v>33</v>
-      </c>
       <c r="U22" s="58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="V22" s="59"/>
       <c r="W22" s="59"/>
       <c r="X22" s="60"/>
       <c r="Y22" s="33"/>
       <c r="Z22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA22" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="49" t="s">
         <v>31</v>
-      </c>
-      <c r="AA22" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB22" s="61"/>
-      <c r="AC22" s="49" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="41" t="s">
         <v>3</v>
@@ -2167,19 +2169,19 @@
         <v>4</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E23" s="33"/>
       <c r="F23" s="44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="81"/>
       <c r="H23" s="81"/>
       <c r="I23" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L23" s="41" t="s">
         <v>3</v>
@@ -2188,19 +2190,19 @@
         <v>4</v>
       </c>
       <c r="N23" s="54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O23" s="33"/>
       <c r="P23" s="44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q23" s="81"/>
       <c r="R23" s="81"/>
       <c r="S23" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U23" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V23" s="41" t="s">
         <v>3</v>
@@ -2209,16 +2211,16 @@
         <v>4</v>
       </c>
       <c r="X23" s="54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Y23" s="33"/>
       <c r="Z23" s="44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA23" s="81"/>
       <c r="AB23" s="81"/>
       <c r="AC23" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
@@ -2230,7 +2232,7 @@
       <c r="D24" s="53"/>
       <c r="E24" s="33"/>
       <c r="F24" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G24" s="77"/>
       <c r="H24" s="77"/>
@@ -2243,7 +2245,7 @@
       <c r="N24" s="53"/>
       <c r="O24" s="33"/>
       <c r="P24" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q24" s="77"/>
       <c r="R24" s="77"/>
@@ -2256,7 +2258,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA24" s="77"/>
       <c r="AB24" s="77"/>
@@ -2271,7 +2273,7 @@
       <c r="D25" s="25"/>
       <c r="E25" s="33"/>
       <c r="F25" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" s="77"/>
       <c r="H25" s="77"/>
@@ -2284,7 +2286,7 @@
       <c r="N25" s="25"/>
       <c r="O25" s="33"/>
       <c r="P25" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q25" s="77"/>
       <c r="R25" s="77"/>
@@ -2297,7 +2299,7 @@
       <c r="X25" s="25"/>
       <c r="Y25" s="33"/>
       <c r="Z25" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AA25" s="77"/>
       <c r="AB25" s="77"/>
@@ -2312,12 +2314,12 @@
       <c r="D26" s="25"/>
       <c r="E26" s="33"/>
       <c r="F26" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G26" s="77"/>
       <c r="H26" s="77"/>
       <c r="I26" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K26" s="9">
         <v>3</v>
@@ -2327,12 +2329,12 @@
       <c r="N26" s="25"/>
       <c r="O26" s="33"/>
       <c r="P26" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q26" s="77"/>
       <c r="R26" s="77"/>
       <c r="S26" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U26" s="9">
         <v>3</v>
@@ -2342,12 +2344,12 @@
       <c r="X26" s="25"/>
       <c r="Y26" s="33"/>
       <c r="Z26" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA26" s="77"/>
       <c r="AB26" s="77"/>
       <c r="AC26" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
@@ -2359,7 +2361,7 @@
       <c r="D27" s="25"/>
       <c r="E27" s="33"/>
       <c r="F27" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
@@ -2372,7 +2374,7 @@
       <c r="N27" s="25"/>
       <c r="O27" s="33"/>
       <c r="P27" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q27" s="77"/>
       <c r="R27" s="77"/>
@@ -2385,7 +2387,7 @@
       <c r="X27" s="25"/>
       <c r="Y27" s="33"/>
       <c r="Z27" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AA27" s="77"/>
       <c r="AB27" s="77"/>
@@ -2400,10 +2402,10 @@
       <c r="D28" s="28"/>
       <c r="E28" s="23"/>
       <c r="F28" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
+        <v>38</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
       <c r="I28" s="14"/>
       <c r="K28" s="8">
         <v>5</v>
@@ -2413,10 +2415,10 @@
       <c r="N28" s="28"/>
       <c r="O28" s="23"/>
       <c r="P28" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q28" s="56"/>
-      <c r="R28" s="56"/>
+        <v>54</v>
+      </c>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
       <c r="S28" s="14"/>
       <c r="U28" s="8">
         <v>5</v>
@@ -2426,28 +2428,28 @@
       <c r="X28" s="28"/>
       <c r="Y28" s="23"/>
       <c r="Z28" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA28" s="56"/>
-      <c r="AB28" s="56"/>
+        <v>54</v>
+      </c>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
       <c r="AC28" s="14"/>
     </row>
     <row r="29" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L30" s="26">
         <v>0</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V30" s="26">
         <v>0</v>
@@ -2455,19 +2457,19 @@
     </row>
     <row r="31" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B31" s="26">
         <v>0</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L31" s="26">
         <v>0</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V31" s="26">
         <v>0</v>
@@ -2490,56 +2492,6 @@
     <row r="46" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="A5:D6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="U1:AC1"/>
-    <mergeCell ref="U5:X6"/>
-    <mergeCell ref="Z5:AC5"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AB6:AB7"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:V11"/>
-    <mergeCell ref="W9:W11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="AA13:AC13"/>
     <mergeCell ref="AA14:AC14"/>
     <mergeCell ref="Z21:AC21"/>
     <mergeCell ref="U22:X22"/>
@@ -2556,6 +2508,56 @@
     <mergeCell ref="P21:S21"/>
     <mergeCell ref="K22:N22"/>
     <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:V11"/>
+    <mergeCell ref="W9:W11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="AA13:AC13"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="U1:AC1"/>
+    <mergeCell ref="U5:X6"/>
+    <mergeCell ref="Z5:AC5"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AC6:AC7"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2601,39 +2603,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="64"/>
-      <c r="K1" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64"/>
-      <c r="U1" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="64"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="K1" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="57"/>
+      <c r="U1" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="57"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2651,7 +2653,7 @@
         <v>46175</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I3" s="6"/>
       <c r="K3" s="4" t="s">
@@ -2661,7 +2663,7 @@
         <v>46175</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S3" s="6"/>
       <c r="U3" s="4" t="s">
@@ -2671,7 +2673,7 @@
         <v>46175</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AC3" s="6"/>
     </row>
@@ -2684,96 +2686,96 @@
       <c r="AC4" s="3"/>
     </row>
     <row r="5" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="67"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="33"/>
       <c r="F5" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G5" s="59"/>
       <c r="H5" s="59"/>
       <c r="I5" s="60"/>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="63"/>
       <c r="O5" s="33"/>
       <c r="P5" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q5" s="59"/>
       <c r="R5" s="59"/>
       <c r="S5" s="60"/>
-      <c r="U5" s="65" t="s">
+      <c r="U5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="63"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA5" s="59"/>
       <c r="AB5" s="59"/>
       <c r="AC5" s="60"/>
     </row>
     <row r="6" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
       <c r="E6" s="33"/>
-      <c r="F6" s="65" t="s">
+      <c r="F6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="71" t="s">
+      <c r="G6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="70"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
       <c r="O6" s="33"/>
-      <c r="P6" s="65" t="s">
+      <c r="P6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="68"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="66"/>
       <c r="Y6" s="33"/>
-      <c r="Z6" s="65" t="s">
+      <c r="Z6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AA6" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB6" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC6" s="71" t="s">
+      <c r="AA6" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB6" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC6" s="67" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2791,10 +2793,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="33"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="72"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="68"/>
       <c r="K7" s="40" t="s">
         <v>6</v>
       </c>
@@ -2808,10 +2810,10 @@
         <v>7</v>
       </c>
       <c r="O7" s="33"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="72"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="68"/>
       <c r="U7" s="40" t="s">
         <v>6</v>
       </c>
@@ -2825,10 +2827,10 @@
         <v>7</v>
       </c>
       <c r="Y7" s="33"/>
-      <c r="Z7" s="68"/>
-      <c r="AA7" s="69"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="72"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="68"/>
     </row>
     <row r="8" spans="1:29" s="7" customFormat="1" ht="44.4" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
@@ -2873,11 +2875,11 @@
     </row>
     <row r="9" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
       <c r="A9" s="76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B9" s="77"/>
       <c r="C9" s="78" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D9" s="80"/>
       <c r="E9" s="33"/>
@@ -2886,11 +2888,11 @@
       <c r="H9" s="20"/>
       <c r="I9" s="12"/>
       <c r="K9" s="76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="L9" s="77"/>
       <c r="M9" s="78" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="N9" s="80"/>
       <c r="O9" s="33"/>
@@ -2899,11 +2901,11 @@
       <c r="R9" s="20"/>
       <c r="S9" s="12"/>
       <c r="U9" s="76" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="V9" s="77"/>
       <c r="W9" s="78" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="X9" s="80"/>
       <c r="Y9" s="33"/>
@@ -2942,28 +2944,28 @@
       <c r="AC10" s="12"/>
     </row>
     <row r="11" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="68"/>
-      <c r="B11" s="56"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="74"/>
       <c r="C11" s="79"/>
-      <c r="D11" s="72"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="33"/>
       <c r="F11" s="13"/>
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="14"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="56"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="74"/>
       <c r="M11" s="79"/>
-      <c r="N11" s="72"/>
+      <c r="N11" s="68"/>
       <c r="O11" s="33"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="27"/>
       <c r="R11" s="27"/>
       <c r="S11" s="14"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="56"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="74"/>
       <c r="W11" s="79"/>
-      <c r="X11" s="72"/>
+      <c r="X11" s="68"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="13"/>
       <c r="AA11" s="27"/>
@@ -3006,41 +3008,41 @@
       <c r="D13" s="33"/>
       <c r="E13" s="33"/>
       <c r="F13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="75"/>
+        <v>10</v>
+      </c>
+      <c r="G13" s="70"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="72"/>
       <c r="K13" s="15"/>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
       <c r="N13" s="33"/>
       <c r="O13" s="33"/>
       <c r="P13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="74"/>
-      <c r="S13" s="75"/>
+        <v>10</v>
+      </c>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
       <c r="U13" s="15"/>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
       <c r="Y13" s="33"/>
       <c r="Z13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA13" s="73"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="75"/>
+        <v>10</v>
+      </c>
+      <c r="AA13" s="70"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="72"/>
     </row>
     <row r="14" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" s="19" t="e">
         <f>B14/B8</f>
@@ -3048,17 +3050,17 @@
       </c>
       <c r="E14" s="33"/>
       <c r="F14" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="55"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="57"/>
+        <v>13</v>
+      </c>
+      <c r="G14" s="73"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
       <c r="K14" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L14" s="24"/>
       <c r="M14" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N14" s="19" t="e">
         <f>L14/L8</f>
@@ -3066,17 +3068,17 @@
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="57"/>
+        <v>13</v>
+      </c>
+      <c r="Q14" s="73"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="75"/>
       <c r="U14" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V14" s="24"/>
       <c r="W14" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X14" s="19" t="e">
         <f>V14/V8</f>
@@ -3084,11 +3086,11 @@
       </c>
       <c r="Y14" s="33"/>
       <c r="Z14" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA14" s="55"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="57"/>
+        <v>13</v>
+      </c>
+      <c r="AA14" s="73"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="75"/>
     </row>
     <row r="15" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
@@ -3126,16 +3128,16 @@
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="I16" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>19</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="33"/>
@@ -3143,16 +3145,16 @@
       <c r="N16" s="33"/>
       <c r="O16" s="33"/>
       <c r="P16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="R16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="18" t="s">
+      <c r="S16" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="S16" s="49" t="s">
-        <v>19</v>
       </c>
       <c r="U16" s="15"/>
       <c r="V16" s="33"/>
@@ -3160,34 +3162,34 @@
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
       <c r="Z16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="AA16" s="18" t="s">
+      <c r="AC16" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="AB16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC16" s="49" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="D17" s="49" t="s">
         <v>21</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>23</v>
       </c>
       <c r="E17" s="33"/>
       <c r="F17" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="48"/>
       <c r="H17" s="37" t="e">
@@ -3196,20 +3198,20 @@
       </c>
       <c r="I17" s="45"/>
       <c r="K17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="N17" s="49" t="s">
         <v>21</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="49" t="s">
-        <v>23</v>
       </c>
       <c r="O17" s="33"/>
       <c r="P17" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="48"/>
       <c r="R17" s="37" t="e">
@@ -3218,20 +3220,20 @@
       </c>
       <c r="S17" s="45"/>
       <c r="U17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="W17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="18" t="s">
+      <c r="X17" s="49" t="s">
         <v>21</v>
-      </c>
-      <c r="W17" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="X17" s="49" t="s">
-        <v>23</v>
       </c>
       <c r="Y17" s="33"/>
       <c r="Z17" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA17" s="48"/>
       <c r="AB17" s="37" t="e">
@@ -3242,7 +3244,7 @@
     </row>
     <row r="18" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="37"/>
       <c r="C18" s="50" t="e">
@@ -3254,7 +3256,7 @@
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="20" t="e">
@@ -3263,7 +3265,7 @@
       </c>
       <c r="I18" s="12"/>
       <c r="K18" s="44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L18" s="37"/>
       <c r="M18" s="50" t="e">
@@ -3275,7 +3277,7 @@
       </c>
       <c r="O18" s="33"/>
       <c r="P18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="10"/>
       <c r="R18" s="20" t="e">
@@ -3284,7 +3286,7 @@
       </c>
       <c r="S18" s="12"/>
       <c r="U18" s="44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V18" s="37"/>
       <c r="W18" s="50" t="e">
@@ -3296,7 +3298,7 @@
       </c>
       <c r="Y18" s="33"/>
       <c r="Z18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA18" s="10"/>
       <c r="AB18" s="20" t="e">
@@ -3307,7 +3309,7 @@
     </row>
     <row r="19" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="30" t="e">
@@ -3319,7 +3321,7 @@
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" s="29"/>
       <c r="H19" s="27" t="e">
@@ -3328,7 +3330,7 @@
       </c>
       <c r="I19" s="14"/>
       <c r="K19" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L19" s="27"/>
       <c r="M19" s="30" t="e">
@@ -3340,7 +3342,7 @@
       </c>
       <c r="O19" s="33"/>
       <c r="P19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q19" s="29"/>
       <c r="R19" s="27" t="e">
@@ -3349,7 +3351,7 @@
       </c>
       <c r="S19" s="14"/>
       <c r="U19" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V19" s="27"/>
       <c r="W19" s="30" t="e">
@@ -3361,7 +3363,7 @@
       </c>
       <c r="Y19" s="33"/>
       <c r="Z19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA19" s="29"/>
       <c r="AB19" s="27" t="e">
@@ -3406,7 +3408,7 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
       <c r="F21" s="58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" s="59"/>
       <c r="H21" s="59"/>
@@ -3417,7 +3419,7 @@
       <c r="N21" s="33"/>
       <c r="O21" s="33"/>
       <c r="P21" s="58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q21" s="59"/>
       <c r="R21" s="59"/>
@@ -3428,7 +3430,7 @@
       <c r="X21" s="33"/>
       <c r="Y21" s="33"/>
       <c r="Z21" s="58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA21" s="59"/>
       <c r="AB21" s="59"/>
@@ -3436,60 +3438,60 @@
     </row>
     <row r="22" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
       <c r="D22" s="60"/>
       <c r="E22" s="33"/>
       <c r="F22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="69"/>
+      <c r="I22" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="61"/>
-      <c r="I22" s="49" t="s">
-        <v>33</v>
-      </c>
       <c r="K22" s="58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L22" s="59"/>
       <c r="M22" s="59"/>
       <c r="N22" s="60"/>
       <c r="O22" s="33"/>
       <c r="P22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" s="69"/>
+      <c r="S22" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="61"/>
-      <c r="S22" s="49" t="s">
-        <v>33</v>
-      </c>
       <c r="U22" s="58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="V22" s="59"/>
       <c r="W22" s="59"/>
       <c r="X22" s="60"/>
       <c r="Y22" s="33"/>
       <c r="Z22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA22" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="49" t="s">
         <v>31</v>
-      </c>
-      <c r="AA22" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB22" s="61"/>
-      <c r="AC22" s="49" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:29" s="7" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="41" t="s">
         <v>3</v>
@@ -3498,19 +3500,19 @@
         <v>4</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E23" s="33"/>
       <c r="F23" s="44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="81"/>
       <c r="H23" s="81"/>
       <c r="I23" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L23" s="41" t="s">
         <v>3</v>
@@ -3519,19 +3521,19 @@
         <v>4</v>
       </c>
       <c r="N23" s="54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O23" s="33"/>
       <c r="P23" s="44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q23" s="81"/>
       <c r="R23" s="81"/>
       <c r="S23" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U23" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V23" s="41" t="s">
         <v>3</v>
@@ -3540,16 +3542,16 @@
         <v>4</v>
       </c>
       <c r="X23" s="54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Y23" s="33"/>
       <c r="Z23" s="44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA23" s="81"/>
       <c r="AB23" s="81"/>
       <c r="AC23" s="45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
@@ -3561,7 +3563,7 @@
       <c r="D24" s="53"/>
       <c r="E24" s="33"/>
       <c r="F24" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G24" s="77"/>
       <c r="H24" s="77"/>
@@ -3574,7 +3576,7 @@
       <c r="N24" s="53"/>
       <c r="O24" s="33"/>
       <c r="P24" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q24" s="77"/>
       <c r="R24" s="77"/>
@@ -3587,7 +3589,7 @@
       <c r="X24" s="53"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA24" s="77"/>
       <c r="AB24" s="77"/>
@@ -3602,7 +3604,7 @@
       <c r="D25" s="25"/>
       <c r="E25" s="33"/>
       <c r="F25" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" s="77"/>
       <c r="H25" s="77"/>
@@ -3615,7 +3617,7 @@
       <c r="N25" s="25"/>
       <c r="O25" s="33"/>
       <c r="P25" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q25" s="77"/>
       <c r="R25" s="77"/>
@@ -3628,7 +3630,7 @@
       <c r="X25" s="25"/>
       <c r="Y25" s="33"/>
       <c r="Z25" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AA25" s="77"/>
       <c r="AB25" s="77"/>
@@ -3643,12 +3645,12 @@
       <c r="D26" s="25"/>
       <c r="E26" s="33"/>
       <c r="F26" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G26" s="77"/>
       <c r="H26" s="77"/>
       <c r="I26" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K26" s="9">
         <v>3</v>
@@ -3658,12 +3660,12 @@
       <c r="N26" s="25"/>
       <c r="O26" s="33"/>
       <c r="P26" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q26" s="77"/>
       <c r="R26" s="77"/>
       <c r="S26" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U26" s="9">
         <v>3</v>
@@ -3673,12 +3675,12 @@
       <c r="X26" s="25"/>
       <c r="Y26" s="33"/>
       <c r="Z26" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA26" s="77"/>
       <c r="AB26" s="77"/>
       <c r="AC26" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.25">
@@ -3690,7 +3692,7 @@
       <c r="D27" s="25"/>
       <c r="E27" s="33"/>
       <c r="F27" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
@@ -3703,7 +3705,7 @@
       <c r="N27" s="25"/>
       <c r="O27" s="33"/>
       <c r="P27" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q27" s="77"/>
       <c r="R27" s="77"/>
@@ -3716,7 +3718,7 @@
       <c r="X27" s="25"/>
       <c r="Y27" s="33"/>
       <c r="Z27" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AA27" s="77"/>
       <c r="AB27" s="77"/>
@@ -3731,10 +3733,10 @@
       <c r="D28" s="28"/>
       <c r="E28" s="23"/>
       <c r="F28" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
+        <v>38</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
       <c r="I28" s="14"/>
       <c r="K28" s="8">
         <v>5</v>
@@ -3744,10 +3746,10 @@
       <c r="N28" s="28"/>
       <c r="O28" s="23"/>
       <c r="P28" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q28" s="56"/>
-      <c r="R28" s="56"/>
+        <v>54</v>
+      </c>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
       <c r="S28" s="14"/>
       <c r="U28" s="8">
         <v>5</v>
@@ -3757,28 +3759,28 @@
       <c r="X28" s="28"/>
       <c r="Y28" s="23"/>
       <c r="Z28" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA28" s="56"/>
-      <c r="AB28" s="56"/>
+        <v>54</v>
+      </c>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
       <c r="AC28" s="14"/>
     </row>
     <row r="29" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L30" s="26">
         <v>0</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V30" s="26">
         <v>0</v>
@@ -3786,19 +3788,19 @@
     </row>
     <row r="31" spans="1:29" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B31" s="26">
         <v>0</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L31" s="26">
         <v>0</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V31" s="26">
         <v>0</v>
@@ -3821,6 +3823,56 @@
     <row r="46" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="Z21:AC21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="AA13:AC13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:V11"/>
+    <mergeCell ref="W9:W11"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="K9:K11"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="K1:S1"/>
@@ -3837,56 +3889,6 @@
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AB6:AB7"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="AA13:AC13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="AA14:AC14"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:V11"/>
-    <mergeCell ref="W9:W11"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="Z21:AC21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="AA28:AB28"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
